--- a/data/trans_orig/SE_ADU-Edad-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2007</t>
+          <t>Sexo adulto elegido en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,47 +768,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>465657</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>467489</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>467489</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>439040</t>
+          <t>436753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>496854</t>
+          <t>496301</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,61%</t>
         </is>
       </c>
     </row>
@@ -846,82 +846,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>492167</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>494064</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>494064</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>464699</t>
+          <t>465252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>522513</t>
+          <t>524800</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,47 +1111,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>623465</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>591</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>625494</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>591</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>625494</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>585692</t>
+          <t>583714</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>660786</t>
+          <t>662252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>733483</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>735489</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>700196</t>
+          <t>698730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>775290</t>
+          <t>777268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,11%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,47 +1454,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>687734</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>658</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>689744</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>689744</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>654693</t>
+          <t>653208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>726489</t>
+          <t>729498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -1532,82 +1532,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>636671</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>638668</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>638668</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>601923</t>
+          <t>598914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673719</t>
+          <t>675204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,47 +1797,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>513674</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>515642</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>515642</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>481556</t>
+          <t>482952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>545942</t>
+          <t>550766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,22%</t>
         </is>
       </c>
     </row>
@@ -1875,82 +1875,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>517092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>519147</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>519147</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>488847</t>
+          <t>484023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>553233</t>
+          <t>551837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,33%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,47 +2140,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>402033</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>403986</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>403986</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376524</t>
+          <t>376590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>433980</t>
+          <t>432637</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -2218,82 +2218,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>384821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>386710</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>392</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>386710</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356716</t>
+          <t>358059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414172</t>
+          <t>414106</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,47 +2483,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>341164</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>342934</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>342934</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>320058</t>
+          <t>317936</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>365944</t>
+          <t>367727</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -2561,82 +2561,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>290736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>292583</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1770</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>292583</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>269573</t>
+          <t>267790</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>315459</t>
+          <t>317581</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,47 +2826,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>331706</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>333908</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,34%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>333908</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>311149</t>
+          <t>311257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>356120</t>
+          <t>356136</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2904,82 +2904,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>208061</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>209883</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2202</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>209883</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>187671</t>
+          <t>187655</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>232642</t>
+          <t>232534</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,47 +3169,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3377229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>3379197</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3297</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3379197</t>
-        </is>
-      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3299203</t>
+          <t>3299502</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3468302</t>
+          <t>3461675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3274586</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3276543</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3187439</t>
+          <t>3194066</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3356538</t>
+          <t>3356239</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2012</t>
+          <t>Sexo adulto elegido en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,47 +3747,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>430230</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>430230</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>400150</t>
+          <t>402647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>458371</t>
+          <t>458200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,81%</t>
         </is>
       </c>
     </row>
@@ -3825,82 +3825,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>454146</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>454146</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426005</t>
+          <t>426176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484226</t>
+          <t>481729</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,47 +4090,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>610255</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>610255</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>576564</t>
+          <t>575759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>650830</t>
+          <t>646876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,86%</t>
         </is>
       </c>
     </row>
@@ -4168,82 +4168,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>685112</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>687087</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>687087</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646512</t>
+          <t>650466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720778</t>
+          <t>721583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,62%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>708807</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>710850</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>671990</t>
+          <t>671472</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>749660</t>
+          <t>747469</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -4511,82 +4511,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>679855</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>681863</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>681863</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643052</t>
+          <t>645243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>720722</t>
+          <t>721240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,75%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,47 +4776,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>614008</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>539</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>616199</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>616199</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>578549</t>
+          <t>577976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>650762</t>
+          <t>652062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -4854,82 +4854,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>612468</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>614617</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2191</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>614617</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>580054</t>
+          <t>578754</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>652267</t>
+          <t>652840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,47 +5119,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>445688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>447800</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>447800</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>417039</t>
+          <t>415422</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>478607</t>
+          <t>478597</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5197,82 +5197,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>427337</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>429429</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>429429</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398622</t>
+          <t>398632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>460190</t>
+          <t>461807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,47 +5462,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>352026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>353996</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>344</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>353996</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>327501</t>
+          <t>324358</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>381590</t>
+          <t>381218</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,43%</t>
         </is>
       </c>
     </row>
@@ -5540,82 +5540,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>307685</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>309786</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1970</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>309786</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>282192</t>
+          <t>282564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>336281</t>
+          <t>339424</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,47 +5805,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>386852</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>388979</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>388979</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>364244</t>
+          <t>362561</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>413551</t>
+          <t>415049</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,97%</t>
         </is>
       </c>
     </row>
@@ -5883,82 +5883,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247701</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>249851</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2127</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>249851</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>225279</t>
+          <t>223781</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274586</t>
+          <t>276269</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,47 +6148,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3556237</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>3558309</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3298</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3558309</t>
-        </is>
-      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3462499</t>
+          <t>3473059</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3637809</t>
+          <t>3648696</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -6226,82 +6226,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3424729</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
           <t>3426779</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3209</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>3426779</t>
-        </is>
-      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3347279</t>
+          <t>3336392</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3522589</t>
+          <t>3512029</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,28%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2016</t>
+          <t>Sexo adulto elegido en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,47 +6726,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>395755</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,53%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>395755</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>366526</t>
+          <t>368676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>424013</t>
+          <t>426624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -6804,82 +6804,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>419463</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>393</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>419463</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>391205</t>
+          <t>388594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>448692</t>
+          <t>446542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,47 +7069,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>563544</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>563544</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>530745</t>
+          <t>529121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>599821</t>
+          <t>596772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,71%</t>
         </is>
       </c>
     </row>
@@ -7147,82 +7147,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>588500</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>567</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>590496</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>567</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>590496</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>554219</t>
+          <t>557268</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>623295</t>
+          <t>624919</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,47 +7412,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>659479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>661386</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>661386</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>625072</t>
+          <t>625420</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>702328</t>
+          <t>699652</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -7490,82 +7490,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>669097</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>669097</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628155</t>
+          <t>630831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>705411</t>
+          <t>705063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,99%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,47 +7755,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>647010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>602</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>649077</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>602</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>649077</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>614338</t>
+          <t>614221</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>688271</t>
+          <t>687297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,07%</t>
         </is>
       </c>
     </row>
@@ -7833,82 +7833,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>643920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>646048</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>646048</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>606854</t>
+          <t>607828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>680787</t>
+          <t>680904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,47 +8098,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>494651</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>496849</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>433</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>496849</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>464421</t>
+          <t>463294</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>529419</t>
+          <t>530107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,38%</t>
         </is>
       </c>
     </row>
@@ -8176,82 +8176,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>475759</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>477918</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>2198</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>477918</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>445348</t>
+          <t>444660</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>510346</t>
+          <t>511473</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,47 +8441,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>375719</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>377762</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>377762</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>349443</t>
+          <t>349366</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>403630</t>
+          <t>405111</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,89%</t>
         </is>
       </c>
     </row>
@@ -8519,82 +8519,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>332361</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>334330</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>325</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>334330</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>308462</t>
+          <t>306981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>362649</t>
+          <t>362726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,32%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,94%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,47 +8784,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>397626</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>400169</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>400169</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>375117</t>
+          <t>373928</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>426343</t>
+          <t>424178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,55%</t>
         </is>
       </c>
     </row>
@@ -8862,82 +8862,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>255370</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>256998</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2543</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>256998</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>230824</t>
+          <t>232989</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>282050</t>
+          <t>283239</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>43,1%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,47 +9127,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3542503</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3338</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>3544542</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3338</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3544542</t>
-        </is>
-      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3466598</t>
+          <t>3459508</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3630980</t>
+          <t>3628134</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,29%</t>
         </is>
       </c>
     </row>
@@ -9205,82 +9205,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3392333</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
           <t>3394350</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>2039</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>3394350</t>
-        </is>
-      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3307912</t>
+          <t>3310758</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3472294</t>
+          <t>3479384</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>50,14%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sexo adulto elegido en 2023</t>
+          <t>Sexo adulto elegido en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,47 +9705,47 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>310311</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
           <t>313200</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>313200</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>276842</t>
+          <t>272048</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>353591</t>
+          <t>353079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,51%</t>
         </is>
       </c>
     </row>
@@ -9783,82 +9783,82 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t>399987</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2889</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>399987</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>359596</t>
+          <t>360108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>436345</t>
+          <t>441139</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,85%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,47 +10048,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>509965</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
           <t>512093</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>512093</t>
-        </is>
-      </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>461259</t>
+          <t>464049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>612613</t>
+          <t>612450</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,46%</t>
         </is>
       </c>
     </row>
@@ -10126,82 +10126,82 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
           <t>423547</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>99,37%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>423547</t>
-        </is>
-      </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323027</t>
+          <t>323190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>474381</t>
+          <t>471591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,4%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,47 +10391,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>590663</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
           <t>592002</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>99,77%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>592002</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>551908</t>
+          <t>554375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>683959</t>
+          <t>662022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>58,67%</t>
         </is>
       </c>
     </row>
@@ -10469,82 +10469,82 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534455</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
           <t>536338</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>546</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>536338</t>
-        </is>
-      </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>444381</t>
+          <t>466318</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>576432</t>
+          <t>573965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,47 +10734,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>711682</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
           <t>712881</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>712881</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>428405</t>
+          <t>459139</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>857101</t>
+          <t>859332</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -10812,82 +10812,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885226</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t>887786</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1199</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>887786</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743566</t>
+          <t>741335</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1172262</t>
+          <t>1141528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,47 +11077,47 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>546856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
           <t>547905</t>
         </is>
       </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>547905</t>
-        </is>
-      </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>518669</t>
+          <t>519520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>573745</t>
+          <t>577895</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -11155,82 +11155,82 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>559611</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
           <t>561234</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1049</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>561234</t>
-        </is>
-      </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>535394</t>
+          <t>531244</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>590470</t>
+          <t>589619</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,16%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1238</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,47 +11420,47 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>606957</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
           <t>608368</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>99,77%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>827</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>608368</t>
-        </is>
-      </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>500007</t>
+          <t>502296</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>766104</t>
+          <t>782490</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -11498,82 +11498,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>366927</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>368165</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>368165</t>
-        </is>
-      </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>210429</t>
+          <t>194043</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>476526</t>
+          <t>474237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1183</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,47 +11763,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>424904</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
           <t>425831</t>
         </is>
       </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>99,78%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>881</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>425831</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>405965</t>
+          <t>407626</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>446946</t>
+          <t>447697</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -11841,82 +11841,82 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>281576</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>282759</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>927</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>458</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>282759</t>
-        </is>
-      </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>261644</t>
+          <t>260893</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>302625</t>
+          <t>300964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,47 +12106,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3710952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>5367</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
           <t>3712280</t>
         </is>
       </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>99,96%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>5367</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3712280</t>
-        </is>
-      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3347397</t>
+          <t>3360210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4010183</t>
+          <t>3998706</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -12184,82 +12184,82 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3457849</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
           <t>3459817</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>99,94%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>3376</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>3459817</t>
-        </is>
-      </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3161914</t>
+          <t>3173391</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3824700</t>
+          <t>3811887</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,15%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/SE_ADU-Edad-trans_orig.xlsx
+++ b/data/trans_orig/SE_ADU-Edad-trans_orig.xlsx
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>436753</t>
+          <t>438575</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>496301</t>
+          <t>496615</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>465252</t>
+          <t>464938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>524800</t>
+          <t>522978</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,39%</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>583714</t>
+          <t>591165</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>662252</t>
+          <t>663528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698730</t>
+          <t>697454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>777268</t>
+          <t>769817</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>653208</t>
+          <t>650334</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>729498</t>
+          <t>725643</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>54,62%</t>
         </is>
       </c>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598914</t>
+          <t>602769</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>675204</t>
+          <t>678078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,04%</t>
         </is>
       </c>
     </row>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>482952</t>
+          <t>480909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>550766</t>
+          <t>547942</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>484023</t>
+          <t>486847</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>551837</t>
+          <t>553880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,53%</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>376590</t>
+          <t>379066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>432637</t>
+          <t>432681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>358059</t>
+          <t>358015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>414106</t>
+          <t>411630</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>317936</t>
+          <t>316768</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>367727</t>
+          <t>367556</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>267790</t>
+          <t>267961</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>317581</t>
+          <t>318749</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,16%</t>
         </is>
       </c>
     </row>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>311257</t>
+          <t>310998</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>356136</t>
+          <t>356055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>187655</t>
+          <t>187736</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>232534</t>
+          <t>232793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,81%</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3299502</t>
+          <t>3291559</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3461675</t>
+          <t>3465110</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3194066</t>
+          <t>3190631</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3356239</t>
+          <t>3364182</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>402647</t>
+          <t>399128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>458200</t>
+          <t>459406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,95%</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426176</t>
+          <t>424970</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>481729</t>
+          <t>485248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,87%</t>
         </is>
       </c>
     </row>
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>575759</t>
+          <t>571944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>646876</t>
+          <t>645652</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,77%</t>
         </is>
       </c>
     </row>
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>650466</t>
+          <t>651690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>721583</t>
+          <t>725398</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>671472</t>
+          <t>672297</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>747469</t>
+          <t>748411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,74%</t>
         </is>
       </c>
     </row>
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645243</t>
+          <t>644301</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>721240</t>
+          <t>720415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>577976</t>
+          <t>576938</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>652062</t>
+          <t>652042</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>578754</t>
+          <t>578774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>652840</t>
+          <t>653878</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,13%</t>
         </is>
       </c>
     </row>
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>415422</t>
+          <t>418349</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>478597</t>
+          <t>481993</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>398632</t>
+          <t>395236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>461807</t>
+          <t>458880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>324358</t>
+          <t>328827</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>381218</t>
+          <t>381290</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>282564</t>
+          <t>282492</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>339424</t>
+          <t>334955</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,46%</t>
         </is>
       </c>
     </row>
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>362561</t>
+          <t>362072</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>415049</t>
+          <t>415414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,03%</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>223781</t>
+          <t>223416</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>276269</t>
+          <t>276758</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,32%</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3473059</t>
+          <t>3474644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3648696</t>
+          <t>3647065</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3336392</t>
+          <t>3338023</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3512029</t>
+          <t>3510444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,26%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>368676</t>
+          <t>368451</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>426624</t>
+          <t>422000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>51,77%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>388594</t>
+          <t>393218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>446542</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>529121</t>
+          <t>526680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>596772</t>
+          <t>596354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>557268</t>
+          <t>557686</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>624919</t>
+          <t>627360</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>625420</t>
+          <t>625992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>699652</t>
+          <t>699768</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>630831</t>
+          <t>630715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>705063</t>
+          <t>704491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>614221</t>
+          <t>611343</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>687297</t>
+          <t>686881</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>607828</t>
+          <t>608244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>680904</t>
+          <t>683782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,8%</t>
         </is>
       </c>
     </row>
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>463294</t>
+          <t>462019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>530107</t>
+          <t>527501</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,12%</t>
         </is>
       </c>
     </row>
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>444660</t>
+          <t>447266</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>511473</t>
+          <t>512748</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,6%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>349366</t>
+          <t>351482</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>405111</t>
+          <t>405393</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>306981</t>
+          <t>306699</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>362726</t>
+          <t>360610</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,64%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>373928</t>
+          <t>374088</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>424178</t>
+          <t>423244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>232989</t>
+          <t>233923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>283239</t>
+          <t>283079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,08%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3459508</t>
+          <t>3458868</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3628134</t>
+          <t>3624708</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3310758</t>
+          <t>3314184</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3479384</t>
+          <t>3480024</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>50,15%</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>272048</t>
+          <t>318732</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>353079</t>
+          <t>402144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9778,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>360108</t>
+          <t>368161</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>441139</t>
+          <t>451573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>58,62%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10043,7 +10043,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>464049</t>
+          <t>463494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>612450</t>
+          <t>540250</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>55,21%</t>
         </is>
       </c>
     </row>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>323190</t>
+          <t>438373</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>471591</t>
+          <t>515129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623192</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>554375</t>
+          <t>590337</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>662022</t>
+          <t>655895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>466318</t>
+          <t>588134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>573965</t>
+          <t>653692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10729,7 +10729,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736887</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>459139</t>
+          <t>702525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>859332</t>
+          <t>772603</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,75%</t>
         </is>
       </c>
     </row>
@@ -10807,7 +10807,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>741335</t>
+          <t>664901</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1141528</t>
+          <t>734979</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>51,13%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>519520</t>
+          <t>580152</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>577895</t>
+          <t>640463</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609347</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>531244</t>
+          <t>577739</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>589619</t>
+          <t>638050</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>502296</t>
+          <t>418340</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>782490</t>
+          <t>462303</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>194043</t>
+          <t>383943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>474237</t>
+          <t>427906</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>407626</t>
+          <t>441749</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>447697</t>
+          <t>485611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,68%</t>
         </is>
       </c>
     </row>
@@ -11836,7 +11836,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260893</t>
+          <t>289196</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>300964</t>
+          <t>333058</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3360210</t>
+          <t>3647018</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3998706</t>
+          <t>3820432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>52,55%</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3173391</t>
+          <t>3449284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3811887</t>
+          <t>3622698</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,15%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
